--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Friends LIbrary Folder/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA34F08-D222-8D4A-802C-DF34D4A87D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00456C39-523F-644F-A7EB-E970E141EABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="50">
   <si>
     <t>S.No.</t>
   </si>
@@ -166,7 +166,10 @@
     <t>Paid</t>
   </si>
   <si>
-    <t>Unpaid</t>
+    <t>Raj</t>
+  </si>
+  <si>
+    <t>Prashant</t>
   </si>
 </sst>
 </file>
@@ -174,7 +177,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -263,7 +266,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -278,7 +281,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -589,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S28"/>
+  <dimension ref="A1:S31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -737,7 +740,9 @@
       <c r="K3" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="7"/>
+      <c r="L3" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
@@ -778,7 +783,7 @@
         <v>47</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
@@ -934,7 +939,9 @@
       <c r="E8" s="5">
         <v>700</v>
       </c>
-      <c r="F8" s="2"/>
+      <c r="F8" s="2">
+        <v>43</v>
+      </c>
       <c r="G8" s="6" t="s">
         <v>21</v>
       </c>
@@ -947,7 +954,9 @@
       <c r="J8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="K8" s="2"/>
+      <c r="K8" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
@@ -974,13 +983,21 @@
         <v>700</v>
       </c>
       <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
+      <c r="G9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="J9" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="K9" s="7"/>
+      <c r="K9" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="L9" s="7"/>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
@@ -1710,7 +1727,7 @@
         <v>47</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -1807,9 +1824,142 @@
       <c r="R28" s="2"/>
       <c r="S28" s="2"/>
     </row>
+    <row r="29" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="4">
+        <v>46170</v>
+      </c>
+      <c r="E29" s="5">
+        <v>700</v>
+      </c>
+      <c r="F29" s="2">
+        <v>13</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2"/>
+    </row>
+    <row r="30" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="4">
+        <v>46174</v>
+      </c>
+      <c r="E30" s="5">
+        <v>700</v>
+      </c>
+      <c r="F30" s="2">
+        <v>50</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
+    </row>
+    <row r="31" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="2">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="4">
+        <v>46174</v>
+      </c>
+      <c r="E31" s="5">
+        <v>700</v>
+      </c>
+      <c r="F31" s="2">
+        <v>49</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="G9 G10 H9 H10 I4 I9 I10 I26 J2 J4 J6 J9 J10 J11 J13 J14 J17 J19 J21 J22 J23 J24 J25 J26 K2 K3 K4 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 L2 L3 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 M2 M3 M4 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 N2 N3 N4 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 O2 O3 O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 P2 P3 P4 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 Q2 Q3 Q4 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q28 R2 R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 S2 S3 S4 S5 S6 S7 S8 S9 S10 S11 S12 S13 S14 S15 S16 S17 S18 S19 S20 S21 S22 S23 S24 S25 S26 S27 S28" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="L2:S31 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 K10:K29" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00456C39-523F-644F-A7EB-E970E141EABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B163B7-442A-0D47-B707-78715544DC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Students" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="51">
   <si>
     <t>S.No.</t>
   </si>
@@ -170,6 +170,9 @@
   </si>
   <si>
     <t>Prashant</t>
+  </si>
+  <si>
+    <t>Naveen</t>
   </si>
 </sst>
 </file>
@@ -592,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S31"/>
+  <dimension ref="A1:S32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1428,7 +1431,9 @@
       <c r="K19" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="L19" s="7"/>
+      <c r="L19" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="M19" s="7"/>
       <c r="N19" s="7"/>
       <c r="O19" s="7"/>
@@ -1488,7 +1493,7 @@
         <v>40</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D21" s="9">
         <v>46119</v>
@@ -1496,9 +1501,7 @@
       <c r="E21" s="10">
         <v>700</v>
       </c>
-      <c r="F21" s="7">
-        <v>4</v>
-      </c>
+      <c r="F21" s="7"/>
       <c r="G21" s="6" t="s">
         <v>21</v>
       </c>
@@ -1514,7 +1517,9 @@
       <c r="K21" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="L21" s="7"/>
+      <c r="L21" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="M21" s="7"/>
       <c r="N21" s="7"/>
       <c r="O21" s="7"/>
@@ -1531,7 +1536,7 @@
         <v>41</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D22" s="4">
         <v>46119</v>
@@ -1557,7 +1562,9 @@
       <c r="K22" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L22" s="2"/>
+      <c r="L22" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -1626,7 +1633,7 @@
         <v>700</v>
       </c>
       <c r="F24" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>21</v>
@@ -1957,9 +1964,54 @@
       <c r="R31" s="2"/>
       <c r="S31" s="2"/>
     </row>
+    <row r="32" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="4">
+        <v>46175</v>
+      </c>
+      <c r="E32" s="5">
+        <v>700</v>
+      </c>
+      <c r="F32" s="2">
+        <v>4</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="L2:S31 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 K10:K29" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 M2:S32 L23:L32 L2:L20" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B163B7-442A-0D47-B707-78715544DC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D2CAEC-207D-EF42-B77A-020C1A7EAF3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="57">
   <si>
     <t>S.No.</t>
   </si>
@@ -173,6 +173,24 @@
   </si>
   <si>
     <t>Naveen</t>
+  </si>
+  <si>
+    <t>Manasvi</t>
+  </si>
+  <si>
+    <t>Manas</t>
+  </si>
+  <si>
+    <t>Anuj</t>
+  </si>
+  <si>
+    <t>Unpaid</t>
+  </si>
+  <si>
+    <t>Vikash</t>
+  </si>
+  <si>
+    <t>Vipin</t>
   </si>
 </sst>
 </file>
@@ -595,7 +613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S32"/>
+  <dimension ref="A1:S37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1147,7 +1165,7 @@
         <v>32</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D13" s="9">
         <v>46121</v>
@@ -1155,9 +1173,7 @@
       <c r="E13" s="10">
         <v>700</v>
       </c>
-      <c r="F13" s="7">
-        <v>35</v>
-      </c>
+      <c r="F13" s="7"/>
       <c r="G13" s="6" t="s">
         <v>21</v>
       </c>
@@ -1173,7 +1189,9 @@
       <c r="K13" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="L13" s="7"/>
+      <c r="L13" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="M13" s="7"/>
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
@@ -1216,7 +1234,9 @@
       <c r="K14" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L14" s="2"/>
+      <c r="L14" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -1544,9 +1564,7 @@
       <c r="E22" s="5">
         <v>700</v>
       </c>
-      <c r="F22" s="2">
-        <v>42</v>
-      </c>
+      <c r="F22" s="2"/>
       <c r="G22" s="6" t="s">
         <v>21</v>
       </c>
@@ -1753,7 +1771,7 @@
         <v>46</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D27" s="9">
         <v>46148</v>
@@ -1761,9 +1779,7 @@
       <c r="E27" s="10">
         <v>700</v>
       </c>
-      <c r="F27" s="7">
-        <v>24</v>
-      </c>
+      <c r="F27" s="7"/>
       <c r="G27" s="6" t="s">
         <v>21</v>
       </c>
@@ -1779,7 +1795,9 @@
       <c r="K27" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="L27" s="7"/>
+      <c r="L27" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
       <c r="O27" s="7"/>
@@ -2009,9 +2027,234 @@
       <c r="R32" s="2"/>
       <c r="S32" s="2"/>
     </row>
+    <row r="33" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="2">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="4">
+        <v>46175</v>
+      </c>
+      <c r="E33" s="5">
+        <v>700</v>
+      </c>
+      <c r="F33" s="2">
+        <v>15</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2"/>
+    </row>
+    <row r="34" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="2">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="4">
+        <v>46180</v>
+      </c>
+      <c r="E34" s="5">
+        <v>700</v>
+      </c>
+      <c r="F34" s="2">
+        <v>12</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
+    </row>
+    <row r="35" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="2">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" s="4">
+        <v>46181</v>
+      </c>
+      <c r="E35" s="5">
+        <v>700</v>
+      </c>
+      <c r="F35" s="2">
+        <v>11</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
+    </row>
+    <row r="36" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="2">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" s="4">
+        <v>46178</v>
+      </c>
+      <c r="E36" s="5">
+        <v>700</v>
+      </c>
+      <c r="F36" s="2">
+        <v>41</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
+    </row>
+    <row r="37" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="2">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="4">
+        <v>46178</v>
+      </c>
+      <c r="E37" s="5">
+        <v>700</v>
+      </c>
+      <c r="F37" s="2">
+        <v>42</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 M2:S32 L23:L32 L2:L20" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 M2:S37 L14:L20 L2:L12 L23:L26 L28:L37" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D2CAEC-207D-EF42-B77A-020C1A7EAF3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DE477D3-2C53-4D4B-AB92-A4A80EBF962D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="56">
   <si>
     <t>S.No.</t>
   </si>
@@ -182,9 +182,6 @@
   </si>
   <si>
     <t>Anuj</t>
-  </si>
-  <si>
-    <t>Unpaid</t>
   </si>
   <si>
     <t>Vikash</t>
@@ -613,7 +610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S37"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1062,7 +1059,9 @@
       <c r="K10" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L10" s="2"/>
+      <c r="L10" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1608,7 +1607,7 @@
         <v>700</v>
       </c>
       <c r="F23" s="7">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>21</v>
@@ -1771,7 +1770,7 @@
         <v>46</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D27" s="9">
         <v>46148</v>
@@ -1779,7 +1778,9 @@
       <c r="E27" s="10">
         <v>700</v>
       </c>
-      <c r="F27" s="7"/>
+      <c r="F27" s="7">
+        <v>9</v>
+      </c>
       <c r="G27" s="6" t="s">
         <v>21</v>
       </c>
@@ -1795,9 +1796,7 @@
       <c r="K27" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="L27" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="L27" s="2"/>
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
       <c r="O27" s="7"/>
@@ -2107,7 +2106,7 @@
         <v>21</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
@@ -2152,7 +2151,7 @@
         <v>21</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
@@ -2167,7 +2166,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>20</v>
@@ -2212,7 +2211,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>20</v>
@@ -2252,9 +2251,54 @@
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
     </row>
+    <row r="38" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" s="4">
+        <v>46180</v>
+      </c>
+      <c r="E38" s="5">
+        <v>700</v>
+      </c>
+      <c r="F38" s="2">
+        <v>34</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 M2:S37 L14:L20 L2:L12 L23:L26 L28:L37" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 M2:S38 L14:L20 L2:L12 L23:L38" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DE477D3-2C53-4D4B-AB92-A4A80EBF962D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759EBDAA-C101-0F41-AB96-786375A2AC69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="56">
   <si>
     <t>S.No.</t>
   </si>
@@ -949,7 +949,7 @@
         <v>26</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D8" s="4">
         <v>46156</v>
@@ -975,7 +975,9 @@
       <c r="K8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L8" s="2"/>
+      <c r="L8" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -2298,7 +2300,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 M2:S38 L14:L20 L2:L12 L23:L38" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 M2:S38 L14:L20 L23:L38 L2:L7 L9:L12" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759EBDAA-C101-0F41-AB96-786375A2AC69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29FAC3BE-B729-4746-8F3A-78DE1798E164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="58">
   <si>
     <t>S.No.</t>
   </si>
@@ -188,6 +188,12 @@
   </si>
   <si>
     <t>Vipin</t>
+  </si>
+  <si>
+    <t>Mohit</t>
+  </si>
+  <si>
+    <t>Sahitya</t>
   </si>
 </sst>
 </file>
@@ -610,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S38"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1123,7 +1129,7 @@
         <v>31</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D12" s="4">
         <v>46157</v>
@@ -1131,9 +1137,7 @@
       <c r="E12" s="5">
         <v>700</v>
       </c>
-      <c r="F12" s="2">
-        <v>19</v>
-      </c>
+      <c r="F12" s="2"/>
       <c r="G12" s="6" t="s">
         <v>21</v>
       </c>
@@ -1149,7 +1153,9 @@
       <c r="K12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L12" s="2"/>
+      <c r="L12" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1297,7 +1303,7 @@
         <v>35</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D16" s="4">
         <v>46157</v>
@@ -1305,9 +1311,7 @@
       <c r="E16" s="5">
         <v>700</v>
       </c>
-      <c r="F16" s="2">
-        <v>20</v>
-      </c>
+      <c r="F16" s="2"/>
       <c r="G16" s="6" t="s">
         <v>21</v>
       </c>
@@ -1323,7 +1327,9 @@
       <c r="K16" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L16" s="2"/>
+      <c r="L16" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -1383,7 +1389,7 @@
         <v>37</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D18" s="4">
         <v>46160</v>
@@ -1391,9 +1397,7 @@
       <c r="E18" s="5">
         <v>700</v>
       </c>
-      <c r="F18" s="2">
-        <v>48</v>
-      </c>
+      <c r="F18" s="2"/>
       <c r="G18" s="6" t="s">
         <v>21</v>
       </c>
@@ -1626,7 +1630,9 @@
       <c r="K23" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="L23" s="7"/>
+      <c r="L23" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="M23" s="7"/>
       <c r="N23" s="7"/>
       <c r="O23" s="7"/>
@@ -1643,7 +1649,7 @@
         <v>43</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D24" s="4">
         <v>46126</v>
@@ -1669,7 +1675,9 @@
       <c r="K24" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L24" s="2"/>
+      <c r="L24" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -2298,9 +2306,99 @@
       <c r="R38" s="2"/>
       <c r="S38" s="2"/>
     </row>
+    <row r="39" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="2">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" s="4">
+        <v>46187</v>
+      </c>
+      <c r="E39" s="5">
+        <v>700</v>
+      </c>
+      <c r="F39" s="2">
+        <v>5</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="2"/>
+      <c r="S39" s="2"/>
+    </row>
+    <row r="40" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="2">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" s="4">
+        <v>46187</v>
+      </c>
+      <c r="E40" s="5">
+        <v>700</v>
+      </c>
+      <c r="F40" s="2">
+        <v>26</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2"/>
+      <c r="S40" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 M2:S38 L14:L20 L23:L38 L2:L7 L9:L12" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 M2:S40 L9:L11 L17:L20 L2:L7 L14:L15 L23 L25:L40" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29FAC3BE-B729-4746-8F3A-78DE1798E164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D51B22C-0F1A-604F-9E86-CC89746596C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="59">
   <si>
     <t>S.No.</t>
   </si>
@@ -194,6 +194,9 @@
   </si>
   <si>
     <t>Sahitya</t>
+  </si>
+  <si>
+    <t>Aamni</t>
   </si>
 </sst>
 </file>
@@ -616,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -2323,7 +2326,7 @@
         <v>700</v>
       </c>
       <c r="F39" s="2">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>21</v>
@@ -2396,9 +2399,54 @@
       <c r="R40" s="2"/>
       <c r="S40" s="2"/>
     </row>
+    <row r="41" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="2">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="4">
+        <v>46189</v>
+      </c>
+      <c r="E41" s="5">
+        <v>700</v>
+      </c>
+      <c r="F41" s="2">
+        <v>19</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="2"/>
+      <c r="S41" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 M2:S40 L9:L11 L17:L20 L2:L7 L14:L15 L23 L25:L40" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 M2:S41 L9:L11 L17:L20 L2:L7 L14:L15 L23 L25:L41" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D51B22C-0F1A-604F-9E86-CC89746596C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F714EF74-9F3A-B74F-A939-69A67459EC6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="59">
   <si>
     <t>S.No.</t>
   </si>
@@ -872,7 +872,7 @@
         <v>24</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D6" s="4">
         <v>46127</v>
@@ -880,9 +880,7 @@
       <c r="E6" s="5">
         <v>700</v>
       </c>
-      <c r="F6" s="2">
-        <v>32</v>
-      </c>
+      <c r="F6" s="2"/>
       <c r="G6" s="6" t="s">
         <v>21</v>
       </c>
@@ -898,7 +896,9 @@
       <c r="K6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L6" s="2"/>
+      <c r="L6" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1809,7 +1809,9 @@
       <c r="K27" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="L27" s="2"/>
+      <c r="L27" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
       <c r="O27" s="7"/>
@@ -2416,7 +2418,7 @@
         <v>700</v>
       </c>
       <c r="F41" s="2">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>21</v>
@@ -2446,7 +2448,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 M2:S41 L9:L11 L17:L20 L2:L7 L14:L15 L23 L25:L41" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 M2:S41 L9:L11 L17:L20 L25:L41 L14:L15 L23 L2:L5 L7" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F714EF74-9F3A-B74F-A939-69A67459EC6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D0D0E2-DA98-0B43-8836-1BF982E20FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="59">
   <si>
     <t>S.No.</t>
   </si>
@@ -1828,7 +1828,7 @@
         <v>29</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D28" s="4">
         <v>46162</v>
@@ -1836,9 +1836,7 @@
       <c r="E28" s="5">
         <v>700</v>
       </c>
-      <c r="F28" s="2">
-        <v>38</v>
-      </c>
+      <c r="F28" s="2"/>
       <c r="G28" s="6" t="s">
         <v>21</v>
       </c>
@@ -1854,7 +1852,9 @@
       <c r="K28" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L28" s="2"/>
+      <c r="L28" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -2448,7 +2448,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 M2:S41 L9:L11 L17:L20 L25:L41 L14:L15 L23 L2:L5 L7" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 M2:S41 L9:L11 L17:L20 L7 L14:L15 L23 L2:L5 L25:L27 L29:L41" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D0D0E2-DA98-0B43-8836-1BF982E20FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A43B816-B582-1B45-B137-1F55C5073164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="59">
   <si>
     <t>S.No.</t>
   </si>
@@ -829,7 +829,7 @@
         <v>23</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D5" s="9">
         <v>46166</v>
@@ -837,9 +837,7 @@
       <c r="E5" s="10">
         <v>700</v>
       </c>
-      <c r="F5" s="7">
-        <v>14</v>
-      </c>
+      <c r="F5" s="7"/>
       <c r="G5" s="6" t="s">
         <v>21</v>
       </c>
@@ -855,7 +853,9 @@
       <c r="K5" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="L5" s="7"/>
+      <c r="L5" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
@@ -915,7 +915,7 @@
         <v>25</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D7" s="9">
         <v>46162</v>
@@ -923,9 +923,7 @@
       <c r="E7" s="10">
         <v>700</v>
       </c>
-      <c r="F7" s="7">
-        <v>37</v>
-      </c>
+      <c r="F7" s="7"/>
       <c r="G7" s="6" t="s">
         <v>21</v>
       </c>
@@ -941,7 +939,9 @@
       <c r="K7" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="L7" s="7"/>
+      <c r="L7" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
@@ -1504,7 +1504,9 @@
       <c r="K20" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L20" s="2"/>
+      <c r="L20" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2448,7 +2450,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 M2:S41 L9:L11 L17:L20 L7 L14:L15 L23 L2:L5 L25:L27 L29:L41" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 M2:S41 L9:L11 L17:L20 L2:L4 L14:L15 L23 L29:L41 L25:L27" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A43B816-B582-1B45-B137-1F55C5073164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5D5DDC-73CF-5D4A-891E-F523C3DE2335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="59">
   <si>
     <t>S.No.</t>
   </si>
@@ -1263,7 +1263,7 @@
         <v>34</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D15" s="9">
         <v>46161</v>
@@ -1271,9 +1271,7 @@
       <c r="E15" s="10">
         <v>700</v>
       </c>
-      <c r="F15" s="7">
-        <v>46</v>
-      </c>
+      <c r="F15" s="7"/>
       <c r="G15" s="6" t="s">
         <v>21</v>
       </c>
@@ -1289,7 +1287,9 @@
       <c r="K15" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="L15" s="7"/>
+      <c r="L15" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
@@ -2450,7 +2450,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 M2:S41 L9:L11 L17:L20 L2:L4 L14:L15 L23 L29:L41 L25:L27" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 M2:S41 L9:L11 L17:L20 L2:L4 L25:L27 L23 L29:L41 L14" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5D5DDC-73CF-5D4A-891E-F523C3DE2335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC2D322B-007F-454C-80A4-DF103DC981D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="60">
   <si>
     <t>S.No.</t>
   </si>
@@ -197,6 +197,9 @@
   </si>
   <si>
     <t>Aamni</t>
+  </si>
+  <si>
+    <t>Pranav A4(outside)</t>
   </si>
 </sst>
 </file>
@@ -619,7 +622,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S41"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -724,7 +727,9 @@
       <c r="K2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="2"/>
+      <c r="L2" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -1098,7 +1103,7 @@
         <v>700</v>
       </c>
       <c r="F11" s="7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>21</v>
@@ -1375,7 +1380,9 @@
       <c r="K17" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="L17" s="7"/>
+      <c r="L17" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
       <c r="O17" s="7"/>
@@ -2448,9 +2455,54 @@
       <c r="R41" s="2"/>
       <c r="S41" s="2"/>
     </row>
+    <row r="42" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" s="4">
+        <v>46196</v>
+      </c>
+      <c r="E42" s="5">
+        <v>700</v>
+      </c>
+      <c r="F42" s="2">
+        <v>30</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="2"/>
+      <c r="S42" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 M2:S41 L9:L11 L17:L20 L2:L4 L25:L27 L23 L29:L41 L14" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 M2:S42 L9:L11 L17:L20 L2:L4 L25:L27 L23 L29:L42 L14" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC2D322B-007F-454C-80A4-DF103DC981D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A19130-01D6-F54F-8C07-D77489DE7A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="61">
   <si>
     <t>S.No.</t>
   </si>
@@ -200,6 +200,9 @@
   </si>
   <si>
     <t>Pranav A4(outside)</t>
+  </si>
+  <si>
+    <t>Rishabh</t>
   </si>
 </sst>
 </file>
@@ -622,7 +625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S42"/>
+  <dimension ref="A1:S44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1008,15 +1011,17 @@
         <v>27</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D9" s="11">
-        <v>45761</v>
+        <v>46203</v>
       </c>
       <c r="E9" s="10">
         <v>700</v>
       </c>
-      <c r="F9" s="7"/>
+      <c r="F9" s="7">
+        <v>1</v>
+      </c>
       <c r="G9" s="6" t="s">
         <v>21</v>
       </c>
@@ -1032,7 +1037,9 @@
       <c r="K9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="L9" s="7"/>
+      <c r="L9" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
@@ -1880,7 +1887,7 @@
         <v>43</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D29" s="4">
         <v>46170</v>
@@ -1888,9 +1895,7 @@
       <c r="E29" s="5">
         <v>700</v>
       </c>
-      <c r="F29" s="2">
-        <v>13</v>
-      </c>
+      <c r="F29" s="2"/>
       <c r="G29" s="6" t="s">
         <v>21</v>
       </c>
@@ -1906,7 +1911,9 @@
       <c r="K29" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L29" s="2"/>
+      <c r="L29" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -2500,9 +2507,99 @@
       <c r="R42" s="2"/>
       <c r="S42" s="2"/>
     </row>
+    <row r="43" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="2">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" s="4">
+        <v>46202</v>
+      </c>
+      <c r="E43" s="5">
+        <v>700</v>
+      </c>
+      <c r="F43" s="2">
+        <v>38</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J43" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M43" s="2"/>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" s="2"/>
+      <c r="Q43" s="2"/>
+      <c r="R43" s="2"/>
+      <c r="S43" s="2"/>
+    </row>
+    <row r="44" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="2">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" s="4">
+        <v>46201</v>
+      </c>
+      <c r="E44" s="5">
+        <v>700</v>
+      </c>
+      <c r="F44" s="2">
+        <v>16</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J44" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M44" s="2"/>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" s="2"/>
+      <c r="Q44" s="2"/>
+      <c r="R44" s="2"/>
+      <c r="S44" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 M2:S42 L9:L11 L17:L20 L2:L4 L25:L27 L23 L29:L42 L14" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 M2:S44 L9:L11 L17:L20 L2:L4 L25:L27 L23 L14 L30:L44" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A19130-01D6-F54F-8C07-D77489DE7A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1774F4BB-DA51-2F41-B1D5-57A522E7D04F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2425,7 +2425,7 @@
         <v>58</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D41" s="4">
         <v>46189</v>
@@ -2433,9 +2433,7 @@
       <c r="E41" s="5">
         <v>700</v>
       </c>
-      <c r="F41" s="2">
-        <v>3</v>
-      </c>
+      <c r="F41" s="2"/>
       <c r="G41" s="6" t="s">
         <v>21</v>
       </c>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1774F4BB-DA51-2F41-B1D5-57A522E7D04F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D38CA9C5-4B9D-0E41-A2B5-B24483441437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="63">
   <si>
     <t>S.No.</t>
   </si>
@@ -203,6 +203,12 @@
   </si>
   <si>
     <t>Rishabh</t>
+  </si>
+  <si>
+    <t>Arsh Khan</t>
+  </si>
+  <si>
+    <t>Pradyumn</t>
   </si>
 </sst>
 </file>
@@ -625,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:S46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1716,7 +1722,7 @@
         <v>20</v>
       </c>
       <c r="D25" s="9">
-        <v>46137</v>
+        <v>46142</v>
       </c>
       <c r="E25" s="10">
         <v>700</v>
@@ -1739,7 +1745,9 @@
       <c r="K25" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="L25" s="7"/>
+      <c r="L25" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="M25" s="7"/>
       <c r="N25" s="7"/>
       <c r="O25" s="7"/>
@@ -2595,9 +2603,99 @@
       <c r="R44" s="2"/>
       <c r="S44" s="2"/>
     </row>
+    <row r="45" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="2">
+        <v>43</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45" s="4">
+        <v>46203</v>
+      </c>
+      <c r="E45" s="5">
+        <v>700</v>
+      </c>
+      <c r="F45" s="2">
+        <v>7</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J45" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K45" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M45" s="2"/>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" s="2"/>
+      <c r="Q45" s="2"/>
+      <c r="R45" s="2"/>
+      <c r="S45" s="2"/>
+    </row>
+    <row r="46" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="2">
+        <v>44</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D46" s="4">
+        <v>46203</v>
+      </c>
+      <c r="E46" s="5">
+        <v>700</v>
+      </c>
+      <c r="F46" s="2">
+        <v>19</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J46" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K46" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M46" s="2"/>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" s="2"/>
+      <c r="Q46" s="2"/>
+      <c r="R46" s="2"/>
+      <c r="S46" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 M2:S44 L9:L11 L17:L20 L2:L4 L25:L27 L23 L14 L30:L44" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 M2:S46 L9:L11 L17:L20 L2:L4 L25:L27 L23 L14 L30:L46" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D38CA9C5-4B9D-0E41-A2B5-B24483441437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49148218-E192-2C4F-95C3-CD5C9F6D33B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="64">
   <si>
     <t>S.No.</t>
   </si>
@@ -209,6 +209,9 @@
   </si>
   <si>
     <t>Pradyumn</t>
+  </si>
+  <si>
+    <t>Unpaid</t>
   </si>
 </sst>
 </file>
@@ -755,7 +758,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D3" s="9">
         <v>46143</v>
@@ -763,9 +766,7 @@
       <c r="E3" s="10">
         <v>700</v>
       </c>
-      <c r="F3" s="7">
-        <v>28</v>
-      </c>
+      <c r="F3" s="7"/>
       <c r="G3" s="6" t="s">
         <v>21</v>
       </c>
@@ -784,7 +785,9 @@
       <c r="L3" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="M3" s="7"/>
+      <c r="M3" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
@@ -826,7 +829,9 @@
       <c r="K4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="2"/>
+      <c r="L4" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1107,7 +1112,7 @@
         <v>30</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D11" s="9">
         <v>46133</v>
@@ -1115,9 +1120,7 @@
       <c r="E11" s="10">
         <v>700</v>
       </c>
-      <c r="F11" s="7">
-        <v>45</v>
-      </c>
+      <c r="F11" s="7"/>
       <c r="G11" s="6" t="s">
         <v>21</v>
       </c>
@@ -1133,7 +1136,9 @@
       <c r="K11" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="L11" s="7"/>
+      <c r="L11" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
@@ -1764,7 +1769,7 @@
         <v>45</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D26" s="4">
         <v>46110</v>
@@ -1772,9 +1777,7 @@
       <c r="E26" s="5">
         <v>700</v>
       </c>
-      <c r="F26" s="2">
-        <v>17</v>
-      </c>
+      <c r="F26" s="2"/>
       <c r="G26" s="6" t="s">
         <v>21</v>
       </c>
@@ -1790,7 +1793,9 @@
       <c r="K26" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L26" s="2"/>
+      <c r="L26" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -1967,7 +1972,9 @@
       <c r="L30" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="M30" s="2"/>
+      <c r="M30" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
@@ -2012,7 +2019,9 @@
       <c r="L31" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="M31" s="2"/>
+      <c r="M31" s="2" t="s">
+        <v>63</v>
+      </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
@@ -2057,7 +2066,9 @@
       <c r="L32" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="M32" s="2"/>
+      <c r="M32" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
@@ -2073,7 +2084,7 @@
         <v>51</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D33" s="4">
         <v>46175</v>
@@ -2081,9 +2092,7 @@
       <c r="E33" s="5">
         <v>700</v>
       </c>
-      <c r="F33" s="2">
-        <v>15</v>
-      </c>
+      <c r="F33" s="2"/>
       <c r="G33" s="6" t="s">
         <v>21</v>
       </c>
@@ -2102,7 +2111,9 @@
       <c r="L33" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="M33" s="2"/>
+      <c r="M33" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
@@ -2665,7 +2676,7 @@
         <v>700</v>
       </c>
       <c r="F46" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>21</v>
@@ -2695,7 +2706,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 M2:S46 L9:L11 L17:L20 L2:L4 L25:L27 L23 L14 L30:L46" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 L30:L46 L17:L20 L2:L4 L9:L10 L23 L14 L25 N2:S46 M2 M4:M32 M34:M46" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49148218-E192-2C4F-95C3-CD5C9F6D33B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE7E3634-B730-D54F-982F-3FD0A14FFD9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="63">
   <si>
     <t>S.No.</t>
   </si>
@@ -209,9 +209,6 @@
   </si>
   <si>
     <t>Pradyumn</t>
-  </si>
-  <si>
-    <t>Unpaid</t>
   </si>
 </sst>
 </file>
@@ -2020,7 +2017,7 @@
         <v>47</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -2084,7 +2081,7 @@
         <v>51</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D33" s="4">
         <v>46175</v>
@@ -2092,7 +2089,9 @@
       <c r="E33" s="5">
         <v>700</v>
       </c>
-      <c r="F33" s="2"/>
+      <c r="F33" s="2">
+        <v>47</v>
+      </c>
       <c r="G33" s="6" t="s">
         <v>21</v>
       </c>
@@ -2111,8 +2110,8 @@
       <c r="L33" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="M33" s="6" t="s">
-        <v>21</v>
+      <c r="M33" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -2706,7 +2705,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 L30:L46 L17:L20 L2:L4 L9:L10 L23 L14 L25 N2:S46 M2 M4:M32 M34:M46" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 L30:L46 L17:L20 L2:L4 L9:L10 L23 L14 L25 N2:S46 M2 M4:M46" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE7E3634-B730-D54F-982F-3FD0A14FFD9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12A91033-6662-3641-8B75-2C2E3A28F890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="63">
   <si>
     <t>S.No.</t>
   </si>
@@ -1267,7 +1267,9 @@
       <c r="L14" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="M14" s="2"/>
+      <c r="M14" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12A91033-6662-3641-8B75-2C2E3A28F890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D946AE01-D66A-C54C-ADE4-F6776F634D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="64">
   <si>
     <t>S.No.</t>
   </si>
@@ -209,6 +209,9 @@
   </si>
   <si>
     <t>Pradyumn</t>
+  </si>
+  <si>
+    <t>Shiva</t>
   </si>
 </sst>
 </file>
@@ -631,7 +634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S46"/>
+  <dimension ref="A1:S47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1486,7 +1489,9 @@
       <c r="L19" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="M19" s="7"/>
+      <c r="M19" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="N19" s="7"/>
       <c r="O19" s="7"/>
       <c r="P19" s="7"/>
@@ -2705,9 +2710,56 @@
       <c r="R46" s="2"/>
       <c r="S46" s="2"/>
     </row>
+    <row r="47" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="2">
+        <v>45</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D47" s="4">
+        <v>46203</v>
+      </c>
+      <c r="E47" s="5">
+        <v>700</v>
+      </c>
+      <c r="F47" s="2">
+        <v>33</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K47" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" s="2"/>
+      <c r="Q47" s="2"/>
+      <c r="R47" s="2"/>
+      <c r="S47" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 L30:L46 L17:L20 L2:L4 L9:L10 L23 L14 L25 N2:S46 M2 M4:M46" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 L30:L47 L17:L20 L2:L4 L9:L10 L23 L14 L25 N2:S47 M2 M4:M47" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D946AE01-D66A-C54C-ADE4-F6776F634D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D80F4FD-39C2-D24D-9AD6-E80ED958772D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="64">
   <si>
     <t>S.No.</t>
   </si>
@@ -160,9 +160,6 @@
     <t>Vivek</t>
   </si>
   <si>
-    <t>Shivam</t>
-  </si>
-  <si>
     <t>Paid</t>
   </si>
   <si>
@@ -212,6 +209,9 @@
   </si>
   <si>
     <t>Shiva</t>
+  </si>
+  <si>
+    <t>Shivang</t>
   </si>
 </sst>
 </file>
@@ -734,13 +734,13 @@
         <v>21</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -780,10 +780,10 @@
         <v>21</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M3" s="6" t="s">
         <v>21</v>
@@ -821,16 +821,16 @@
         <v>21</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
@@ -870,7 +870,7 @@
         <v>21</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>21</v>
@@ -910,10 +910,10 @@
         <v>21</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>21</v>
@@ -956,7 +956,7 @@
         <v>21</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>21</v>
@@ -1001,7 +1001,7 @@
         <v>21</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>21</v>
@@ -1043,13 +1043,13 @@
         <v>21</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K9" s="6" t="s">
         <v>21</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
@@ -1079,22 +1079,22 @@
         <v>39</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
@@ -1131,10 +1131,10 @@
         <v>21</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>21</v>
@@ -1177,7 +1177,7 @@
         <v>21</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>21</v>
@@ -1217,10 +1217,10 @@
         <v>21</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>21</v>
@@ -1262,16 +1262,16 @@
         <v>21</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -1310,7 +1310,7 @@
         <v>21</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>21</v>
@@ -1353,7 +1353,7 @@
         <v>21</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>21</v>
@@ -1395,13 +1395,13 @@
         <v>21</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
@@ -1441,7 +1441,7 @@
         <v>21</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -1481,16 +1481,16 @@
         <v>21</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N19" s="7"/>
       <c r="O19" s="7"/>
@@ -1531,10 +1531,10 @@
         <v>21</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
@@ -1571,10 +1571,10 @@
         <v>21</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>21</v>
@@ -1614,10 +1614,10 @@
         <v>21</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L22" s="6" t="s">
         <v>21</v>
@@ -1659,13 +1659,13 @@
         <v>21</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M23" s="7"/>
       <c r="N23" s="7"/>
@@ -1704,10 +1704,10 @@
         <v>21</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L24" s="6" t="s">
         <v>21</v>
@@ -1749,13 +1749,13 @@
         <v>21</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M25" s="7"/>
       <c r="N25" s="7"/>
@@ -1789,13 +1789,13 @@
         <v>21</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L26" s="6" t="s">
         <v>21</v>
@@ -1813,13 +1813,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D27" s="9">
-        <v>46148</v>
+        <v>46152</v>
       </c>
       <c r="E27" s="10">
         <v>700</v>
@@ -1840,10 +1840,10 @@
         <v>21</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
@@ -1883,7 +1883,7 @@
         <v>21</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L28" s="6" t="s">
         <v>21</v>
@@ -1926,7 +1926,7 @@
         <v>21</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L29" s="6" t="s">
         <v>21</v>
@@ -1944,7 +1944,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>20</v>
@@ -1974,10 +1974,10 @@
         <v>21</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -1991,7 +1991,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>20</v>
@@ -2021,10 +2021,10 @@
         <v>21</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -2038,7 +2038,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>20</v>
@@ -2068,10 +2068,10 @@
         <v>21</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -2085,7 +2085,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>20</v>
@@ -2115,10 +2115,10 @@
         <v>21</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -2132,7 +2132,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>20</v>
@@ -2162,7 +2162,7 @@
         <v>21</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
@@ -2177,7 +2177,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>20</v>
@@ -2207,7 +2207,7 @@
         <v>21</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
@@ -2222,10 +2222,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D36" s="4">
         <v>46178</v>
@@ -2233,9 +2233,7 @@
       <c r="E36" s="5">
         <v>700</v>
       </c>
-      <c r="F36" s="2">
-        <v>41</v>
-      </c>
+      <c r="F36" s="2"/>
       <c r="G36" s="6" t="s">
         <v>21</v>
       </c>
@@ -2252,9 +2250,11 @@
         <v>21</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M36" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" s="2"/>
@@ -2267,10 +2267,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D37" s="4">
         <v>46178</v>
@@ -2278,9 +2278,7 @@
       <c r="E37" s="5">
         <v>700</v>
       </c>
-      <c r="F37" s="2">
-        <v>42</v>
-      </c>
+      <c r="F37" s="2"/>
       <c r="G37" s="6" t="s">
         <v>21</v>
       </c>
@@ -2297,9 +2295,11 @@
         <v>21</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M37" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
@@ -2342,7 +2342,7 @@
         <v>21</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
@@ -2357,7 +2357,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>20</v>
@@ -2387,7 +2387,7 @@
         <v>21</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
@@ -2402,7 +2402,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>20</v>
@@ -2432,7 +2432,7 @@
         <v>21</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
@@ -2447,7 +2447,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>28</v>
@@ -2475,7 +2475,7 @@
         <v>21</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
@@ -2490,7 +2490,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>20</v>
@@ -2520,7 +2520,7 @@
         <v>21</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
@@ -2535,7 +2535,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>20</v>
@@ -2565,7 +2565,7 @@
         <v>21</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
@@ -2610,7 +2610,7 @@
         <v>21</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
@@ -2625,7 +2625,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>20</v>
@@ -2655,7 +2655,7 @@
         <v>21</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
@@ -2670,7 +2670,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>20</v>
@@ -2700,7 +2700,7 @@
         <v>21</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
@@ -2715,7 +2715,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>20</v>
@@ -2745,10 +2745,10 @@
         <v>21</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -2759,7 +2759,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 L30:L47 L17:L20 L2:L4 L9:L10 L23 L14 L25 N2:S47 M2 M4:M47" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 L30:L47 L17:L20 L2:L4 L9:L10 L23 L14 L25 N2:S47 M2 M4:M35 M38:M47" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D80F4FD-39C2-D24D-9AD6-E80ED958772D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{678833A4-6AC1-884E-800D-8E686932DDAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="67">
   <si>
     <t>S.No.</t>
   </si>
@@ -212,6 +212,15 @@
   </si>
   <si>
     <t>Shivang</t>
+  </si>
+  <si>
+    <t>Afnan</t>
+  </si>
+  <si>
+    <t>Aayan</t>
+  </si>
+  <si>
+    <t>Deependra</t>
   </si>
 </sst>
 </file>
@@ -634,7 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S47"/>
+  <dimension ref="A1:S50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1647,7 +1656,7 @@
         <v>700</v>
       </c>
       <c r="F23" s="7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>21</v>
@@ -2164,7 +2173,9 @@
       <c r="L34" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="2"/>
+      <c r="M34" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
@@ -2180,7 +2191,7 @@
         <v>52</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D35" s="4">
         <v>46181</v>
@@ -2188,9 +2199,7 @@
       <c r="E35" s="5">
         <v>700</v>
       </c>
-      <c r="F35" s="2">
-        <v>11</v>
-      </c>
+      <c r="F35" s="2"/>
       <c r="G35" s="6" t="s">
         <v>21</v>
       </c>
@@ -2209,7 +2218,9 @@
       <c r="L35" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M35" s="2"/>
+      <c r="M35" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
@@ -2344,7 +2355,9 @@
       <c r="L38" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M38" s="2"/>
+      <c r="M38" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
@@ -2757,9 +2770,150 @@
       <c r="R47" s="2"/>
       <c r="S47" s="2"/>
     </row>
+    <row r="48" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="2">
+        <v>46</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D48" s="4">
+        <v>46214</v>
+      </c>
+      <c r="E48" s="5">
+        <v>700</v>
+      </c>
+      <c r="F48" s="2">
+        <v>18</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J48" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K48" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="2"/>
+      <c r="R48" s="2"/>
+      <c r="S48" s="2"/>
+    </row>
+    <row r="49" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="2">
+        <v>47</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D49" s="4">
+        <v>46214</v>
+      </c>
+      <c r="E49" s="5">
+        <v>700</v>
+      </c>
+      <c r="F49" s="2">
+        <v>19</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J49" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K49" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L49" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" s="2"/>
+      <c r="Q49" s="2"/>
+      <c r="R49" s="2"/>
+      <c r="S49" s="2"/>
+    </row>
+    <row r="50" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="2">
+        <v>48</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D50" s="4">
+        <v>46211</v>
+      </c>
+      <c r="E50" s="5">
+        <v>700</v>
+      </c>
+      <c r="F50" s="2">
+        <v>44</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J50" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" s="2"/>
+      <c r="Q50" s="2"/>
+      <c r="R50" s="2"/>
+      <c r="S50" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 L30:L47 L17:L20 L2:L4 L9:L10 L23 L14 L25 N2:S47 M2 M4:M35 M38:M47" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 M38:M50 L17:L20 L2:L4 L9:L10 L23 L14 L25 N2:S50 M2 L30:L47 M4:M34" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{678833A4-6AC1-884E-800D-8E686932DDAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E5972B-251D-8D4A-9E1B-07852D71E0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="69">
   <si>
     <t>S.No.</t>
   </si>
@@ -221,6 +221,12 @@
   </si>
   <si>
     <t>Deependra</t>
+  </si>
+  <si>
+    <t>Akansha</t>
+  </si>
+  <si>
+    <t>Aaryan</t>
   </si>
 </sst>
 </file>
@@ -643,7 +649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S50"/>
+  <dimension ref="A1:S52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -2590,7 +2596,7 @@
     </row>
     <row r="44" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>29</v>
@@ -2635,7 +2641,7 @@
     </row>
     <row r="45" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>60</v>
@@ -2680,7 +2686,7 @@
     </row>
     <row r="46" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>61</v>
@@ -2725,7 +2731,7 @@
     </row>
     <row r="47" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>62</v>
@@ -2772,7 +2778,7 @@
     </row>
     <row r="48" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>64</v>
@@ -2819,7 +2825,7 @@
     </row>
     <row r="49" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>65</v>
@@ -2866,7 +2872,7 @@
     </row>
     <row r="50" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>66</v>
@@ -2911,9 +2917,103 @@
       <c r="R50" s="2"/>
       <c r="S50" s="2"/>
     </row>
+    <row r="51" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="2">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D51" s="4">
+        <v>46208</v>
+      </c>
+      <c r="E51" s="5">
+        <v>700</v>
+      </c>
+      <c r="F51" s="2">
+        <v>41</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J51" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K51" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L51" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" s="2"/>
+      <c r="Q51" s="2"/>
+      <c r="R51" s="2"/>
+      <c r="S51" s="2"/>
+    </row>
+    <row r="52" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="2">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D52" s="4">
+        <v>46208</v>
+      </c>
+      <c r="E52" s="5">
+        <v>700</v>
+      </c>
+      <c r="F52" s="2">
+        <v>42</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J52" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K52" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L52" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" s="2"/>
+      <c r="Q52" s="2"/>
+      <c r="R52" s="2"/>
+      <c r="S52" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 M38:M50 L17:L20 L2:L4 L9:L10 L23 L14 L25 N2:S50 M2 L30:L47 M4:M34" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 M38:M52 L17:L20 L2:L4 L9:L10 L23 L14 L25 N2:S52 M2 L30:L47 M4:M34" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E5972B-251D-8D4A-9E1B-07852D71E0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB973B3D-5F5E-714D-8C83-658D483785EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="69">
   <si>
     <t>S.No.</t>
   </si>
@@ -1111,7 +1111,9 @@
       <c r="L10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M10" s="2"/>
+      <c r="M10" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB973B3D-5F5E-714D-8C83-658D483785EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464A8122-2C65-2642-B874-6D2F8FB6B2CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="70">
   <si>
     <t>S.No.</t>
   </si>
@@ -227,6 +227,9 @@
   </si>
   <si>
     <t>Aaryan</t>
+  </si>
+  <si>
+    <t>Shreya</t>
   </si>
 </sst>
 </file>
@@ -649,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S52"/>
+  <dimension ref="A1:S53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -3013,9 +3016,56 @@
       <c r="R52" s="2"/>
       <c r="S52" s="2"/>
     </row>
+    <row r="53" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="2">
+        <v>52</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D53" s="4">
+        <v>46217</v>
+      </c>
+      <c r="E53" s="5">
+        <v>700</v>
+      </c>
+      <c r="F53" s="2">
+        <v>28</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J53" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K53" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L53" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" s="2"/>
+      <c r="Q53" s="2"/>
+      <c r="R53" s="2"/>
+      <c r="S53" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 M38:M52 L17:L20 L2:L4 L9:L10 L23 L14 L25 N2:S52 M2 L30:L47 M4:M34" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 M38:M53 L17:L20 L2:L4 L9:L10 L23 L14 L25 N2:S53 M2 L30:L47 M4:M34" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464A8122-2C65-2642-B874-6D2F8FB6B2CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D04EF23-025F-0A46-B5EF-E26975B17B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="73">
   <si>
     <t>S.No.</t>
   </si>
@@ -230,6 +230,15 @@
   </si>
   <si>
     <t>Shreya</t>
+  </si>
+  <si>
+    <t>Nandini</t>
+  </si>
+  <si>
+    <t>Siddhi</t>
+  </si>
+  <si>
+    <t>Vinayak</t>
   </si>
 </sst>
 </file>
@@ -652,7 +661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S53"/>
+  <dimension ref="A1:S56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -2164,7 +2173,7 @@
         <v>700</v>
       </c>
       <c r="F34" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>21</v>
@@ -2429,7 +2438,7 @@
         <v>56</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D40" s="4">
         <v>46187</v>
@@ -2437,9 +2446,7 @@
       <c r="E40" s="5">
         <v>700</v>
       </c>
-      <c r="F40" s="2">
-        <v>26</v>
-      </c>
+      <c r="F40" s="2"/>
       <c r="G40" s="6" t="s">
         <v>21</v>
       </c>
@@ -2458,7 +2465,9 @@
       <c r="L40" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M40" s="2"/>
+      <c r="M40" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
@@ -3063,9 +3072,150 @@
       <c r="R53" s="2"/>
       <c r="S53" s="2"/>
     </row>
+    <row r="54" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="2">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D54" s="4">
+        <v>46217</v>
+      </c>
+      <c r="E54" s="5">
+        <v>700</v>
+      </c>
+      <c r="F54" s="2">
+        <v>12</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J54" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K54" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M54" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" s="2"/>
+      <c r="Q54" s="2"/>
+      <c r="R54" s="2"/>
+      <c r="S54" s="2"/>
+    </row>
+    <row r="55" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="2">
+        <v>54</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D55" s="4">
+        <v>46218</v>
+      </c>
+      <c r="E55" s="5">
+        <v>700</v>
+      </c>
+      <c r="F55" s="2">
+        <v>26</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J55" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K55" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L55" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M55" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" s="2"/>
+      <c r="Q55" s="2"/>
+      <c r="R55" s="2"/>
+      <c r="S55" s="2"/>
+    </row>
+    <row r="56" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="2">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D56" s="4">
+        <v>46218</v>
+      </c>
+      <c r="E56" s="5">
+        <v>700</v>
+      </c>
+      <c r="F56" s="2">
+        <v>27</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J56" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K56" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L56" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" s="2"/>
+      <c r="Q56" s="2"/>
+      <c r="R56" s="2"/>
+      <c r="S56" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 M38:M53 L17:L20 L2:L4 L9:L10 L23 L14 L25 N2:S53 M2 L30:L47 M4:M34" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 M4:M34 L17:L20 L2:L4 L9:L10 L23 L14 L25 N2:S56 M2 L30:L47 M38:M39 M41:M56" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D04EF23-025F-0A46-B5EF-E26975B17B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BDAD193-1C4D-C644-9604-2CE3253E4C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="73">
   <si>
     <t>S.No.</t>
   </si>
@@ -1874,7 +1874,9 @@
       <c r="L27" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M27" s="7"/>
+      <c r="M27" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="N27" s="7"/>
       <c r="O27" s="7"/>
       <c r="P27" s="7"/>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BDAD193-1C4D-C644-9604-2CE3253E4C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E0A714A-C3AC-834E-9E35-0CAC2D897507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="74">
   <si>
     <t>S.No.</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t>Vinayak</t>
+  </si>
+  <si>
+    <t>Satvinder Singh</t>
   </si>
 </sst>
 </file>
@@ -661,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S56"/>
+  <dimension ref="A1:S57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1565,7 +1568,9 @@
       <c r="L20" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M20" s="2"/>
+      <c r="M20" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -1696,7 +1701,9 @@
       <c r="L23" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M23" s="7"/>
+      <c r="M23" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="N23" s="7"/>
       <c r="O23" s="7"/>
       <c r="P23" s="7"/>
@@ -2424,7 +2431,9 @@
       <c r="L39" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M39" s="2"/>
+      <c r="M39" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
@@ -3215,9 +3224,56 @@
       <c r="R56" s="2"/>
       <c r="S56" s="2"/>
     </row>
+    <row r="57" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="2">
+        <v>56</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D57" s="4">
+        <v>46223</v>
+      </c>
+      <c r="E57" s="5">
+        <v>700</v>
+      </c>
+      <c r="F57" s="2">
+        <v>45</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J57" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K57" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L57" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" s="2"/>
+      <c r="Q57" s="2"/>
+      <c r="R57" s="2"/>
+      <c r="S57" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 M4:M34 L17:L20 L2:L4 L9:L10 L23 L14 L25 N2:S56 M2 L30:L47 M38:M39 M41:M56" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 M4:M34 L17:L20 L2:L4 L9:L10 L23 L14 L25 N2:S57 M2 L30:L47 M38:M39 M41:M57" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E0A714A-C3AC-834E-9E35-0CAC2D897507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A833CE0D-BE39-0147-A318-6D902B8AE527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="75">
   <si>
     <t>S.No.</t>
   </si>
@@ -242,6 +242,9 @@
   </si>
   <si>
     <t>Satvinder Singh</t>
+  </si>
+  <si>
+    <t>Nitish Gupta</t>
   </si>
 </sst>
 </file>
@@ -664,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S57"/>
+  <dimension ref="A1:S58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -3241,7 +3244,7 @@
         <v>700</v>
       </c>
       <c r="F57" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>21</v>
@@ -3271,9 +3274,56 @@
       <c r="R57" s="2"/>
       <c r="S57" s="2"/>
     </row>
+    <row r="58" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="2">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D58" s="4">
+        <v>46223</v>
+      </c>
+      <c r="E58" s="5">
+        <v>700</v>
+      </c>
+      <c r="F58" s="2">
+        <v>32</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J58" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" s="2"/>
+      <c r="Q58" s="2"/>
+      <c r="R58" s="2"/>
+      <c r="S58" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 M4:M34 L17:L20 L2:L4 L9:L10 L23 L14 L25 N2:S57 M2 L30:L47 M38:M39 M41:M57" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 M4:M34 L17:L20 L2:L4 L9:L10 L23 L14 L25 N2:S58 M2 L30:L47 M38:M39 M41:M58" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A833CE0D-BE39-0147-A318-6D902B8AE527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{880EEC1C-0C65-2641-A090-737E71914E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="76">
   <si>
     <t>S.No.</t>
   </si>
@@ -139,18 +139,12 @@
     <t>Ravi</t>
   </si>
   <si>
-    <t>Rohan</t>
-  </si>
-  <si>
     <t>Shubhi</t>
   </si>
   <si>
     <t>Simran</t>
   </si>
   <si>
-    <t>Soumya</t>
-  </si>
-  <si>
     <t>Sumit</t>
   </si>
   <si>
@@ -163,18 +157,9 @@
     <t>Paid</t>
   </si>
   <si>
-    <t>Raj</t>
-  </si>
-  <si>
-    <t>Prashant</t>
-  </si>
-  <si>
     <t>Naveen</t>
   </si>
   <si>
-    <t>Manasvi</t>
-  </si>
-  <si>
     <t>Manas</t>
   </si>
   <si>
@@ -211,9 +196,6 @@
     <t>Shiva</t>
   </si>
   <si>
-    <t>Shivang</t>
-  </si>
-  <si>
     <t>Afnan</t>
   </si>
   <si>
@@ -241,10 +223,31 @@
     <t>Vinayak</t>
   </si>
   <si>
-    <t>Satvinder Singh</t>
-  </si>
-  <si>
     <t>Nitish Gupta</t>
+  </si>
+  <si>
+    <t>Soumya(RC)</t>
+  </si>
+  <si>
+    <t>Shivang(RC)</t>
+  </si>
+  <si>
+    <t>Satvinder Singh(RC)</t>
+  </si>
+  <si>
+    <t>Satvinder Singh(brother RC)</t>
+  </si>
+  <si>
+    <t>Manasvi(RC)</t>
+  </si>
+  <si>
+    <t>Rohan(RC)</t>
+  </si>
+  <si>
+    <t>Raj(RC)</t>
+  </si>
+  <si>
+    <t>Prashant(RC)</t>
   </si>
 </sst>
 </file>
@@ -667,11 +670,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S58"/>
+  <dimension ref="A1:S60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="2" max="2" width="23.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
@@ -767,13 +770,13 @@
         <v>21</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -813,10 +816,10 @@
         <v>21</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M3" s="6" t="s">
         <v>21</v>
@@ -845,7 +848,7 @@
         <v>700</v>
       </c>
       <c r="F4" s="2">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>21</v>
@@ -854,16 +857,16 @@
         <v>21</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
@@ -903,7 +906,7 @@
         <v>21</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>21</v>
@@ -943,10 +946,10 @@
         <v>21</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>21</v>
@@ -989,7 +992,7 @@
         <v>21</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>21</v>
@@ -1034,7 +1037,7 @@
         <v>21</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>21</v>
@@ -1076,13 +1079,13 @@
         <v>21</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K9" s="6" t="s">
         <v>21</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
@@ -1112,25 +1115,25 @@
         <v>39</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1166,10 +1169,10 @@
         <v>21</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>21</v>
@@ -1212,7 +1215,7 @@
         <v>21</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>21</v>
@@ -1252,10 +1255,10 @@
         <v>21</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>21</v>
@@ -1282,7 +1285,7 @@
         <v>46117</v>
       </c>
       <c r="E14" s="5">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="F14" s="2">
         <v>8</v>
@@ -1297,16 +1300,16 @@
         <v>21</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -1345,7 +1348,7 @@
         <v>21</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>21</v>
@@ -1388,7 +1391,7 @@
         <v>21</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>21</v>
@@ -1430,13 +1433,13 @@
         <v>21</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
@@ -1476,7 +1479,7 @@
         <v>21</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -1516,16 +1519,16 @@
         <v>21</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N19" s="7"/>
       <c r="O19" s="7"/>
@@ -1539,7 +1542,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>20</v>
@@ -1548,7 +1551,7 @@
         <v>46161</v>
       </c>
       <c r="E20" s="5">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="F20" s="2">
         <v>36</v>
@@ -1566,13 +1569,13 @@
         <v>21</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -1586,7 +1589,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>28</v>
@@ -1608,10 +1611,10 @@
         <v>21</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>21</v>
@@ -1629,7 +1632,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>28</v>
@@ -1651,10 +1654,10 @@
         <v>21</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L22" s="6" t="s">
         <v>21</v>
@@ -1672,7 +1675,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>20</v>
@@ -1696,16 +1699,16 @@
         <v>21</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N23" s="7"/>
       <c r="O23" s="7"/>
@@ -1719,7 +1722,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
@@ -1743,10 +1746,10 @@
         <v>21</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L24" s="6" t="s">
         <v>21</v>
@@ -1764,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>20</v>
@@ -1788,13 +1791,13 @@
         <v>21</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M25" s="7"/>
       <c r="N25" s="7"/>
@@ -1809,7 +1812,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>28</v>
@@ -1828,13 +1831,13 @@
         <v>21</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L26" s="6" t="s">
         <v>21</v>
@@ -1852,7 +1855,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>20</v>
@@ -1861,7 +1864,7 @@
         <v>46152</v>
       </c>
       <c r="E27" s="10">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="F27" s="7">
         <v>9</v>
@@ -1879,13 +1882,13 @@
         <v>21</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N27" s="7"/>
       <c r="O27" s="7"/>
@@ -1924,7 +1927,7 @@
         <v>21</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L28" s="6" t="s">
         <v>21</v>
@@ -1942,7 +1945,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>28</v>
@@ -1967,7 +1970,7 @@
         <v>21</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L29" s="6" t="s">
         <v>21</v>
@@ -1985,7 +1988,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>20</v>
@@ -2015,10 +2018,10 @@
         <v>21</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -2032,7 +2035,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>20</v>
@@ -2062,10 +2065,10 @@
         <v>21</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -2079,7 +2082,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>20</v>
@@ -2109,10 +2112,10 @@
         <v>21</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -2126,7 +2129,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>20</v>
@@ -2135,7 +2138,7 @@
         <v>46175</v>
       </c>
       <c r="E33" s="5">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="F33" s="2">
         <v>47</v>
@@ -2156,10 +2159,10 @@
         <v>21</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -2173,7 +2176,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>20</v>
@@ -2203,10 +2206,10 @@
         <v>21</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -2220,7 +2223,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>28</v>
@@ -2248,7 +2251,7 @@
         <v>21</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>21</v>
@@ -2265,7 +2268,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>28</v>
@@ -2293,7 +2296,7 @@
         <v>21</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>21</v>
@@ -2310,7 +2313,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>28</v>
@@ -2338,7 +2341,7 @@
         <v>21</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>21</v>
@@ -2385,10 +2388,10 @@
         <v>21</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -2402,7 +2405,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>20</v>
@@ -2432,10 +2435,10 @@
         <v>21</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -2449,7 +2452,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>28</v>
@@ -2477,7 +2480,7 @@
         <v>21</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>21</v>
@@ -2494,7 +2497,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>28</v>
@@ -2522,7 +2525,7 @@
         <v>21</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
@@ -2537,10 +2540,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D42" s="4">
         <v>46196</v>
@@ -2548,9 +2551,7 @@
       <c r="E42" s="5">
         <v>700</v>
       </c>
-      <c r="F42" s="2">
-        <v>30</v>
-      </c>
+      <c r="F42" s="2"/>
       <c r="G42" s="6" t="s">
         <v>21</v>
       </c>
@@ -2567,7 +2568,7 @@
         <v>21</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
@@ -2582,7 +2583,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>20</v>
@@ -2612,7 +2613,7 @@
         <v>21</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
@@ -2657,7 +2658,7 @@
         <v>21</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
@@ -2672,10 +2673,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D45" s="4">
         <v>46203</v>
@@ -2683,9 +2684,7 @@
       <c r="E45" s="5">
         <v>700</v>
       </c>
-      <c r="F45" s="2">
-        <v>7</v>
-      </c>
+      <c r="F45" s="2"/>
       <c r="G45" s="6" t="s">
         <v>21</v>
       </c>
@@ -2702,9 +2701,11 @@
         <v>21</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M45" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="M45" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" s="2"/>
@@ -2717,7 +2718,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>20</v>
@@ -2747,7 +2748,7 @@
         <v>21</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
@@ -2762,7 +2763,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>20</v>
@@ -2792,10 +2793,10 @@
         <v>21</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -2809,7 +2810,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>20</v>
@@ -2842,7 +2843,7 @@
         <v>21</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -2856,7 +2857,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>20</v>
@@ -2889,7 +2890,7 @@
         <v>21</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -2903,7 +2904,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>20</v>
@@ -2936,7 +2937,7 @@
         <v>21</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -2950,7 +2951,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>20</v>
@@ -2983,7 +2984,7 @@
         <v>21</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -2997,7 +2998,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>20</v>
@@ -3030,7 +3031,7 @@
         <v>21</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -3044,7 +3045,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>20</v>
@@ -3077,7 +3078,7 @@
         <v>21</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -3091,7 +3092,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>20</v>
@@ -3124,7 +3125,7 @@
         <v>21</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -3138,7 +3139,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>20</v>
@@ -3171,7 +3172,7 @@
         <v>21</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -3185,7 +3186,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>20</v>
@@ -3218,7 +3219,7 @@
         <v>21</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -3232,7 +3233,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>20</v>
@@ -3241,7 +3242,7 @@
         <v>46223</v>
       </c>
       <c r="E57" s="5">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="F57" s="2">
         <v>37</v>
@@ -3265,7 +3266,7 @@
         <v>21</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -3279,7 +3280,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>20</v>
@@ -3312,7 +3313,7 @@
         <v>21</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -3321,9 +3322,103 @@
       <c r="R58" s="2"/>
       <c r="S58" s="2"/>
     </row>
+    <row r="59" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="2">
+        <v>58</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D59" s="4">
+        <v>46228</v>
+      </c>
+      <c r="E59" s="5">
+        <v>700</v>
+      </c>
+      <c r="F59" s="2">
+        <v>45</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J59" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K59" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L59" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M59" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" s="2"/>
+      <c r="Q59" s="2"/>
+      <c r="R59" s="2"/>
+      <c r="S59" s="2"/>
+    </row>
+    <row r="60" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="2">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D60" s="4">
+        <v>46223</v>
+      </c>
+      <c r="E60" s="5">
+        <v>800</v>
+      </c>
+      <c r="F60" s="2">
+        <v>46</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J60" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K60" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L60" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" s="2"/>
+      <c r="Q60" s="2"/>
+      <c r="R60" s="2"/>
+      <c r="S60" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 M4:M34 L17:L20 L2:L4 L9:L10 L23 L14 L25 N2:S58 M2 L30:L47 M38:M39 M41:M58" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 M4:M34 L17:L20 L2:L4 L9:L10 L23 L14 L25 N2:S60 M2 L30:L47 M38:M39 M41:M44 M46:M60" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{880EEC1C-0C65-2641-A090-737E71914E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BEAAA1B-7528-6D45-AADC-56FF2DDB75A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="76">
   <si>
     <t>S.No.</t>
   </si>
@@ -778,7 +778,9 @@
       <c r="L2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M2" s="2"/>
+      <c r="M2" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
@@ -1441,7 +1443,9 @@
       <c r="L17" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="M17" s="7"/>
+      <c r="M17" s="7" t="s">
+        <v>44</v>
+      </c>
       <c r="N17" s="7"/>
       <c r="O17" s="7"/>
       <c r="P17" s="7"/>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BEAAA1B-7528-6D45-AADC-56FF2DDB75A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E52E070E-EB6C-5645-8BDA-B4DCC71E32F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2770,7 +2770,7 @@
         <v>57</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D47" s="4">
         <v>46203</v>
@@ -2778,9 +2778,7 @@
       <c r="E47" s="5">
         <v>700</v>
       </c>
-      <c r="F47" s="2">
-        <v>33</v>
-      </c>
+      <c r="F47" s="2"/>
       <c r="G47" s="6" t="s">
         <v>21</v>
       </c>
@@ -3296,7 +3294,7 @@
         <v>700</v>
       </c>
       <c r="F58" s="2">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>21</v>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E52E070E-EB6C-5645-8BDA-B4DCC71E32F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E696DBE-6E25-0744-A35A-6DD4E7A04E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="78">
   <si>
     <t>S.No.</t>
   </si>
@@ -229,9 +229,6 @@
     <t>Soumya(RC)</t>
   </si>
   <si>
-    <t>Shivang(RC)</t>
-  </si>
-  <si>
     <t>Satvinder Singh(RC)</t>
   </si>
   <si>
@@ -248,6 +245,15 @@
   </si>
   <si>
     <t>Prashant(RC)</t>
+  </si>
+  <si>
+    <t>Shivang</t>
+  </si>
+  <si>
+    <t>Rishabh Kumar(RC)</t>
+  </si>
+  <si>
+    <t>Priya(RC)</t>
   </si>
 </sst>
 </file>
@@ -670,7 +676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S60"/>
+  <dimension ref="A1:S62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1546,7 +1552,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>20</v>
@@ -1803,7 +1809,9 @@
       <c r="L25" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="M25" s="7"/>
+      <c r="M25" s="7" t="s">
+        <v>44</v>
+      </c>
       <c r="N25" s="7"/>
       <c r="O25" s="7"/>
       <c r="P25" s="7"/>
@@ -1859,7 +1867,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>20</v>
@@ -1868,7 +1876,7 @@
         <v>46152</v>
       </c>
       <c r="E27" s="10">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="F27" s="7">
         <v>9</v>
@@ -1992,7 +2000,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>20</v>
@@ -2039,7 +2047,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>20</v>
@@ -2133,7 +2141,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>20</v>
@@ -2635,7 +2643,7 @@
         <v>29</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D44" s="4">
         <v>46201</v>
@@ -2643,9 +2651,7 @@
       <c r="E44" s="5">
         <v>700</v>
       </c>
-      <c r="F44" s="2">
-        <v>16</v>
-      </c>
+      <c r="F44" s="2"/>
       <c r="G44" s="6" t="s">
         <v>21</v>
       </c>
@@ -2664,7 +2670,9 @@
       <c r="L44" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M44" s="2"/>
+      <c r="M44" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" s="2"/>
@@ -2725,7 +2733,7 @@
         <v>56</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D46" s="4">
         <v>46203</v>
@@ -2733,9 +2741,7 @@
       <c r="E46" s="5">
         <v>700</v>
       </c>
-      <c r="F46" s="2">
-        <v>20</v>
-      </c>
+      <c r="F46" s="2"/>
       <c r="G46" s="6" t="s">
         <v>21</v>
       </c>
@@ -3106,7 +3112,7 @@
         <v>700</v>
       </c>
       <c r="F54" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>21</v>
@@ -3235,7 +3241,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>20</v>
@@ -3376,7 +3382,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>20</v>
@@ -3418,9 +3424,103 @@
       <c r="R60" s="2"/>
       <c r="S60" s="2"/>
     </row>
+    <row r="61" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="2">
+        <v>60</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D61" s="4">
+        <v>46230</v>
+      </c>
+      <c r="E61" s="5">
+        <v>800</v>
+      </c>
+      <c r="F61" s="2">
+        <v>31</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J61" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K61" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L61" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M61" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" s="2"/>
+      <c r="Q61" s="2"/>
+      <c r="R61" s="2"/>
+      <c r="S61" s="2"/>
+    </row>
+    <row r="62" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="2">
+        <v>61</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D62" s="4">
+        <v>46234</v>
+      </c>
+      <c r="E62" s="5">
+        <v>800</v>
+      </c>
+      <c r="F62" s="2">
+        <v>48</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J62" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K62" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" s="2"/>
+      <c r="Q62" s="2"/>
+      <c r="R62" s="2"/>
+      <c r="S62" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 M4:M34 L17:L20 L2:L4 L9:L10 L23 L14 L25 N2:S60 M2 L30:L47 M38:M39 M41:M44 M46:M60" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 M4:M34 L17:L20 L2:L4 L9:L10 L23 L14 L25 N2:S62 M2 L30:L47 M38:M39 M46:M62 M41:M43" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E696DBE-6E25-0744-A35A-6DD4E7A04E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35A2DD0-4911-2C44-A0F1-CC6A506CB113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="78">
   <si>
     <t>S.No.</t>
   </si>
@@ -876,7 +876,9 @@
       <c r="L4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M4" s="2"/>
+      <c r="M4" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
@@ -1540,7 +1542,9 @@
       <c r="M19" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="N19" s="7"/>
+      <c r="N19" s="7" t="s">
+        <v>44</v>
+      </c>
       <c r="O19" s="7"/>
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
@@ -2056,7 +2060,7 @@
         <v>46174</v>
       </c>
       <c r="E31" s="5">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="F31" s="2">
         <v>49</v>
@@ -2082,7 +2086,9 @@
       <c r="M31" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="N31" s="2"/>
+      <c r="N31" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
       <c r="Q31" s="2"/>
@@ -2129,7 +2135,9 @@
       <c r="M32" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="N32" s="2"/>
+      <c r="N32" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
       <c r="Q32" s="2"/>
@@ -2176,7 +2184,9 @@
       <c r="M33" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="N33" s="2"/>
+      <c r="N33" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
       <c r="Q33" s="2"/>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35A2DD0-4911-2C44-A0F1-CC6A506CB113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19187729-B629-4440-8502-8535FB04C42E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="80">
   <si>
     <t>S.No.</t>
   </si>
@@ -254,6 +254,12 @@
   </si>
   <si>
     <t>Priya(RC)</t>
+  </si>
+  <si>
+    <t>Harshita</t>
+  </si>
+  <si>
+    <t>Khalid</t>
   </si>
 </sst>
 </file>
@@ -676,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S62"/>
+  <dimension ref="A1:S65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1031,9 +1037,7 @@
       <c r="E8" s="5">
         <v>700</v>
       </c>
-      <c r="F8" s="2">
-        <v>43</v>
-      </c>
+      <c r="F8" s="2"/>
       <c r="G8" s="6" t="s">
         <v>21</v>
       </c>
@@ -1052,7 +1056,9 @@
       <c r="L8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M8" s="2"/>
+      <c r="M8" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
@@ -1068,7 +1074,7 @@
         <v>27</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D9" s="11">
         <v>46203</v>
@@ -1076,9 +1082,7 @@
       <c r="E9" s="10">
         <v>700</v>
       </c>
-      <c r="F9" s="7">
-        <v>1</v>
-      </c>
+      <c r="F9" s="7"/>
       <c r="G9" s="6" t="s">
         <v>21</v>
       </c>
@@ -1097,7 +1101,9 @@
       <c r="L9" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="M9" s="7"/>
+      <c r="M9" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
@@ -1336,7 +1342,7 @@
         <v>34</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D15" s="9">
         <v>46161</v>
@@ -1344,7 +1350,9 @@
       <c r="E15" s="10">
         <v>700</v>
       </c>
-      <c r="F15" s="7"/>
+      <c r="F15" s="7">
+        <v>2</v>
+      </c>
       <c r="G15" s="6" t="s">
         <v>21</v>
       </c>
@@ -2248,7 +2256,7 @@
         <v>47</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D35" s="4">
         <v>46181</v>
@@ -2256,7 +2264,9 @@
       <c r="E35" s="5">
         <v>700</v>
       </c>
-      <c r="F35" s="2"/>
+      <c r="F35" s="2">
+        <v>12</v>
+      </c>
       <c r="G35" s="6" t="s">
         <v>21</v>
       </c>
@@ -2637,7 +2647,9 @@
       <c r="L43" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M43" s="2"/>
+      <c r="M43" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" s="2"/>
@@ -3528,9 +3540,152 @@
       <c r="R62" s="2"/>
       <c r="S62" s="2"/>
     </row>
+    <row r="63" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="2">
+        <v>62</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D63" s="4">
+        <v>46233</v>
+      </c>
+      <c r="E63" s="5">
+        <v>700</v>
+      </c>
+      <c r="F63" s="2">
+        <v>43</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J63" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K63" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L63" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M63" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" s="2"/>
+      <c r="Q63" s="2"/>
+      <c r="R63" s="2"/>
+      <c r="S63" s="2"/>
+    </row>
+    <row r="64" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="2">
+        <v>63</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D64" s="4">
+        <v>46228</v>
+      </c>
+      <c r="E64" s="5">
+        <v>700</v>
+      </c>
+      <c r="F64" s="2">
+        <v>13</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J64" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K64" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L64" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M64" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" s="2"/>
+      <c r="Q64" s="2"/>
+      <c r="R64" s="2"/>
+      <c r="S64" s="2"/>
+    </row>
+    <row r="65" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="2">
+        <v>64</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D65" s="4">
+        <v>46239</v>
+      </c>
+      <c r="E65" s="5">
+        <v>700</v>
+      </c>
+      <c r="F65" s="2">
+        <v>15</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J65" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K65" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L65" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M65" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N65" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" s="2"/>
+      <c r="Q65" s="2"/>
+      <c r="R65" s="2"/>
+      <c r="S65" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 M4:M34 L17:L20 L2:L4 L9:L10 L23 L14 L25 N2:S62 M2 L30:L47 M38:M39 M46:M62 M41:M43" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 M41:M43 L17:L20 L2:L4 L9:L10 L23 L14 L25 M4:M7 M2 L30:L47 M38:M39 N2:S65 M10:M34 M46:M64" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19187729-B629-4440-8502-8535FB04C42E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CABDB427-EEE9-8D4C-98B1-3CB72A6EBE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="80">
   <si>
     <t>S.No.</t>
   </si>
@@ -1345,7 +1345,7 @@
         <v>20</v>
       </c>
       <c r="D15" s="9">
-        <v>46161</v>
+        <v>46236</v>
       </c>
       <c r="E15" s="10">
         <v>700</v>
@@ -1371,8 +1371,12 @@
       <c r="L15" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
+      <c r="M15" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>44</v>
+      </c>
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
@@ -3685,7 +3689,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 M41:M43 L17:L20 L2:L4 L9:L10 L23 L14 L25 M4:M7 M2 L30:L47 M38:M39 N2:S65 M10:M34 M46:M64" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 M41:M43 L17:L20 L2:L4 L9:L10 L23 L14 L25 M4:M7 M2 L30:L47 M38:M39 N2:S65 M46:M64 M10:M14 M16:M34" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CABDB427-EEE9-8D4C-98B1-3CB72A6EBE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3633FE74-7E94-104A-881C-4ED40FE11709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="81">
   <si>
     <t>S.No.</t>
   </si>
@@ -260,6 +260,9 @@
   </si>
   <si>
     <t>Khalid</t>
+  </si>
+  <si>
+    <t>Shivam Singh(Sumit)</t>
   </si>
 </sst>
 </file>
@@ -682,7 +685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S65"/>
+  <dimension ref="A1:S66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -3020,7 +3023,9 @@
       <c r="M51" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="N51" s="2"/>
+      <c r="N51" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" s="2"/>
       <c r="Q51" s="2"/>
@@ -3067,7 +3072,9 @@
       <c r="M52" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="N52" s="2"/>
+      <c r="N52" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" s="2"/>
       <c r="Q52" s="2"/>
@@ -3687,9 +3694,58 @@
       <c r="R65" s="2"/>
       <c r="S65" s="2"/>
     </row>
+    <row r="66" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="2">
+        <v>65</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D66" s="4">
+        <v>46237</v>
+      </c>
+      <c r="E66" s="5">
+        <v>700</v>
+      </c>
+      <c r="F66" s="2">
+        <v>32</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J66" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K66" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L66" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M66" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" s="2"/>
+      <c r="Q66" s="2"/>
+      <c r="R66" s="2"/>
+      <c r="S66" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 M41:M43 L17:L20 L2:L4 L9:L10 L23 L14 L25 M4:M7 M2 L30:L47 M38:M39 N2:S65 M46:M64 M10:M14 M16:M34" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 M41:M43 L17:L20 L2:L4 L9:L10 L23 L14 L25 M4:M7 M2 L30:L47 M38:M39 N2:S66 M46:M64 M10:M14 M16:M34" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3633FE74-7E94-104A-881C-4ED40FE11709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04F64C58-BA09-0149-95D9-AB42196DDAAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4500" yWindow="500" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Students" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="81">
   <si>
     <t>S.No.</t>
   </si>
@@ -2054,7 +2054,9 @@
       <c r="M30" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="N30" s="2"/>
+      <c r="N30" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>

--- a/public/Students_Final.xlsx
+++ b/public/Students_Final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swapnilbaranwal/Desktop/Important documents/friends-library_bareilly/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04F64C58-BA09-0149-95D9-AB42196DDAAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B89BC1C-1214-4F40-913C-AFE5F369B5CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4500" yWindow="500" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Students" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="81">
   <si>
     <t>S.No.</t>
   </si>
@@ -2265,7 +2265,7 @@
         <v>47</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D35" s="4">
         <v>46181</v>
@@ -2273,9 +2273,7 @@
       <c r="E35" s="5">
         <v>700</v>
       </c>
-      <c r="F35" s="2">
-        <v>12</v>
-      </c>
+      <c r="F35" s="2"/>
       <c r="G35" s="6" t="s">
         <v>21</v>
       </c>
@@ -2297,7 +2295,9 @@
       <c r="M35" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="N35" s="2"/>
+      <c r="N35" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
@@ -2411,7 +2411,7 @@
         <v>700</v>
       </c>
       <c r="F38" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>21</v>
@@ -3747,7 +3747,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 M41:M43 L17:L20 L2:L4 L9:L10 L23 L14 L25 M4:M7 M2 L30:L47 M38:M39 N2:S66 M46:M64 M10:M14 M16:M34" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K29 I26 J2 I4:J4 J6 J9:J11 J13:J14 J17 J19 J21:J26 G10:I10 K2:K8 L27 M41:M43 L17:L20 L2:L4 L9:L10 L23 L14 L25 M4:M7 M2 L30:L47 M38:M39 M16:M34 M46:M64 M10:M14 O2:S66 N2:N34 N36:N66" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
   </dataValidations>
